--- a/03_Group_comparisons/Proteome_T2/c_data/03_set_contrasts.xlsx
+++ b/03_Group_comparisons/Proteome_T2/c_data/03_set_contrasts.xlsx
@@ -10475,7 +10475,7 @@
     <t>03_Group_comparisons/Proteome_T2/c_data/02_fit.rds</t>
   </si>
   <si>
-    <t>3202a5435a20130b881f51bf010d4f74</t>
+    <t>5c3207dad2c8de59b447e34c4fb0f338</t>
   </si>
   <si>
     <t>design</t>
@@ -10484,13 +10484,13 @@
     <t>03_Group_comparisons/Proteome_T2/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>ec109143c9337576f3039e2d1550a7c0</t>
+    <t>8ea3f088a35b7fea575e289be5d64c01</t>
   </si>
   <si>
     <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
   </si>
   <si>
-    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
+    <t>015331bb453caea36bcabbe182b7eac6</t>
   </si>
   <si>
     <t>singscore</t>
@@ -10508,7 +10508,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
